--- a/device-model-indicators/磁力矩器_指标库_20260226.xlsx
+++ b/device-model-indicators/磁力矩器_指标库_20260226.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="216" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="260" uniqueCount="47">
   <si>
     <t>型号 Model</t>
   </si>
@@ -1272,9 +1272,7 @@
       <c r="C30" s="0">
         <v>0.080000000000000002</v>
       </c>
-      <c r="D30" s="0">
-        <v>0.5</v>
-      </c>
+      <c r="D30" s="0"/>
       <c r="E30" s="0">
         <v>5</v>
       </c>
@@ -1285,21 +1283,15 @@
       <c r="H30" s="0">
         <v>1.2</v>
       </c>
-      <c r="I30" s="0">
-        <v>1.2</v>
-      </c>
+      <c r="I30" s="0"/>
       <c r="J30" s="0">
         <v>12</v>
       </c>
       <c r="K30" s="0">
         <v>0.29999999999999999</v>
       </c>
-      <c r="L30" s="0">
-        <v>-20</v>
-      </c>
-      <c r="M30" s="0">
-        <v>50</v>
-      </c>
+      <c r="L30" s="0"/>
+      <c r="M30" s="0"/>
       <c r="N30" s="0">
         <v>8</v>
       </c>
@@ -1311,29 +1303,17 @@
       <c r="B31" s="0">
         <v>90</v>
       </c>
-      <c r="C31" s="0">
-        <v>0.90000000000000002</v>
-      </c>
-      <c r="D31" s="0">
-        <v>1</v>
-      </c>
-      <c r="E31" s="0">
-        <v>5</v>
-      </c>
+      <c r="C31" s="0"/>
+      <c r="D31" s="0"/>
+      <c r="E31" s="0"/>
       <c r="F31" s="0"/>
-      <c r="G31" s="0">
-        <v>360</v>
-      </c>
+      <c r="G31" s="0"/>
       <c r="H31" s="0"/>
-      <c r="I31" s="0">
-        <v>1.2</v>
-      </c>
+      <c r="I31" s="0"/>
       <c r="J31" s="0">
         <v>12</v>
       </c>
-      <c r="K31" s="0">
-        <v>2.5</v>
-      </c>
+      <c r="K31" s="0"/>
       <c r="L31" s="0">
         <v>-15</v>
       </c>

--- a/device-model-indicators/磁力矩器_指标库_20260226.xlsx
+++ b/device-model-indicators/磁力矩器_指标库_20260226.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="260" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="304" uniqueCount="49">
   <si>
     <t>型号 Model</t>
   </si>
@@ -154,6 +154,12 @@
   </si>
   <si>
     <t>YYMQ9MGTQ90Am2</t>
+  </si>
+  <si>
+    <t>LX630MGTQ10Am2</t>
+  </si>
+  <si>
+    <t>YYMQ9MGTQ75Am2</t>
   </si>
 </sst>
 </file>
@@ -530,7 +536,7 @@
         <v>5</v>
       </c>
       <c r="K9" s="0">
-        <v>0.14999999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="L9" s="0">
         <v>-20</v>
@@ -674,7 +680,7 @@
         <v>12</v>
       </c>
       <c r="K13" s="0">
-        <v>0.41999999999999998</v>
+        <v>0.41999999999999999</v>
       </c>
       <c r="L13" s="0">
         <v>-20</v>
@@ -730,7 +736,7 @@
         <v>15</v>
       </c>
       <c r="C15" s="0">
-        <v>0.14999999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="D15" s="0"/>
       <c r="E15" s="0"/>
@@ -1264,13 +1270,13 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B30" s="0">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C30" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="D30" s="0"/>
       <c r="E30" s="0">
@@ -1278,30 +1284,30 @@
       </c>
       <c r="F30" s="0"/>
       <c r="G30" s="0">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="H30" s="0">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="I30" s="0"/>
       <c r="J30" s="0">
         <v>12</v>
       </c>
       <c r="K30" s="0">
-        <v>0.29999999999999999</v>
+        <v>0.35999999999999999</v>
       </c>
       <c r="L30" s="0"/>
       <c r="M30" s="0"/>
       <c r="N30" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B31" s="0">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C31" s="0"/>
       <c r="D31" s="0"/>
@@ -1321,7 +1327,7 @@
         <v>50</v>
       </c>
       <c r="N31" s="0">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
